--- a/data/trans_orig/P07B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según salud mental autopercibida en 2023</t>
+          <t>Población según salud mental autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48807</t>
+          <t>48615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62995</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101249</t>
+          <t>100227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129419</t>
+          <t>127827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143575</t>
+          <t>146247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183434</t>
+          <t>183955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237253</t>
+          <t>238453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280655</t>
+          <t>281528</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>404348</t>
+          <t>404549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446144</t>
+          <t>447554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>656384</t>
+          <t>659448</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>718316</t>
+          <t>714481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122793</t>
+          <t>121892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163366</t>
+          <t>161800</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130899</t>
+          <t>130849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164053</t>
+          <t>163439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265296</t>
+          <t>264912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>315727</t>
+          <t>313418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>39046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64590</t>
+          <t>67352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59277</t>
+          <t>57871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75088</t>
+          <t>77552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112984</t>
+          <t>112960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>41450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61437</t>
+          <t>60328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112787</t>
+          <t>114364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126881</t>
+          <t>128277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>451979</t>
+          <t>428631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212894</t>
+          <t>212717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>518790</t>
+          <t>557686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>898523</t>
+          <t>892129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1437901</t>
+          <t>1447631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>879077</t>
+          <t>874590</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1361940</t>
+          <t>1312076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1806937</t>
+          <t>1814899</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2581574</t>
+          <t>2592511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,25%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>527535</t>
+          <t>511696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>862952</t>
+          <t>860879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>526114</t>
+          <t>520436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>806431</t>
+          <t>808122</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1149674</t>
+          <t>1139511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1629475</t>
+          <t>1620532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261038</t>
+          <t>253529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>438812</t>
+          <t>440618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211938</t>
+          <t>212879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375317</t>
+          <t>374391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525739</t>
+          <t>522137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>767100</t>
+          <t>769384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>19981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>23985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49468</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20919</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40277</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80635</t>
+          <t>83798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>239173</t>
+          <t>239561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>291826</t>
+          <t>290725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>238218</t>
+          <t>237476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>281940</t>
+          <t>281022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>487672</t>
+          <t>488647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>555217</t>
+          <t>559093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>199826</t>
+          <t>201296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>251166</t>
+          <t>255257</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226049</t>
+          <t>226977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>272923</t>
+          <t>273178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>442738</t>
+          <t>438419</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>510646</t>
+          <t>508218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96290</t>
+          <t>95862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>150383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,47 +2561,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>14,83%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>115352</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>98354</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>133782</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>14,89%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>22,62%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>115352</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>97790</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>133040</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>203968</t>
+          <t>205097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269576</t>
+          <t>267114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44659</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>60066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>62725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96951</t>
+          <t>96543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>137160</t>
+          <t>134753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204312</t>
+          <t>205772</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>269540</t>
+          <t>274562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>619777</t>
+          <t>572730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>440344</t>
+          <t>434878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>844878</t>
+          <t>745494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1422356</t>
+          <t>1420945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2014215</t>
+          <t>1982282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1562521</t>
+          <t>1559188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2070178</t>
+          <t>2058334</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3038221</t>
+          <t>3033676</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3790194</t>
+          <t>3770403</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>877088</t>
+          <t>882060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1229328</t>
+          <t>1226566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>898170</t>
+          <t>903576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1199905</t>
+          <t>1200734</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1943244</t>
+          <t>1924680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2378222</t>
+          <t>2398106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>431392</t>
+          <t>422776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>615863</t>
+          <t>612537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>373031</t>
+          <t>367253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>544219</t>
+          <t>534854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>854375</t>
+          <t>865760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1107982</t>
+          <t>1112570</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P07B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>35585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>41546</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>52119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49791</t>
+          <t>52934</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>66971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114473</t>
+          <t>126599</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>110981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127827</t>
+          <t>142201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>164263</t>
+          <t>179533</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146247</t>
+          <t>160512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183955</t>
+          <t>202520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>260526</t>
+          <t>283445</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238453</t>
+          <t>259570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>281528</t>
+          <t>305847</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>426288</t>
+          <t>462567</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>404549</t>
+          <t>440919</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447554</t>
+          <t>484745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686813</t>
+          <t>746012</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>659448</t>
+          <t>714533</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>714481</t>
+          <t>779730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>141323</t>
+          <t>157613</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121892</t>
+          <t>136338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161800</t>
+          <t>182095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>146357</t>
+          <t>161201</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130849</t>
+          <t>143287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163439</t>
+          <t>178378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>287681</t>
+          <t>318813</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264912</t>
+          <t>291127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313418</t>
+          <t>345325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50317</t>
+          <t>69891</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39046</t>
+          <t>54073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67352</t>
+          <t>91229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>44771</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>93693</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77552</t>
+          <t>95946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112960</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>43977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89486</t>
+          <t>94017</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>75139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114364</t>
+          <t>116033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>206639</t>
+          <t>149461</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128277</t>
+          <t>130346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>428631</t>
+          <t>173134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>296125</t>
+          <t>243477</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212717</t>
+          <t>218027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>557686</t>
+          <t>276458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1060605</t>
+          <t>906503</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>892129</t>
+          <t>852656</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1447631</t>
+          <t>954890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1023982</t>
+          <t>922674</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>874590</t>
+          <t>881213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1312076</t>
+          <t>968298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2084588</t>
+          <t>1829177</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1814899</t>
+          <t>1759960</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2592511</t>
+          <t>1894413</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>750817</t>
+          <t>831256</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>511696</t>
+          <t>780677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>860879</t>
+          <t>884249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>709083</t>
+          <t>793389</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>520436</t>
+          <t>751470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>808122</t>
+          <t>836698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1459900</t>
+          <t>1624646</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1139511</t>
+          <t>1561203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1620532</t>
+          <t>1693624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>374651</t>
+          <t>383289</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253529</t>
+          <t>335939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440618</t>
+          <t>428759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>283409</t>
+          <t>289747</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212879</t>
+          <t>259696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374391</t>
+          <t>324801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>658059</t>
+          <t>673037</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>522137</t>
+          <t>619737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>769384</t>
+          <t>732113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,22 +2159,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>37769</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40204</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>62931</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83798</t>
+          <t>89169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>265274</t>
+          <t>292843</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>239561</t>
+          <t>262181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>290725</t>
+          <t>319684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258003</t>
+          <t>295951</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>272409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>281022</t>
+          <t>321309</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>523277</t>
+          <t>588794</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>488647</t>
+          <t>551309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>559093</t>
+          <t>629252</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>225167</t>
+          <t>249189</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>201296</t>
+          <t>221667</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>255257</t>
+          <t>279368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>250998</t>
+          <t>271001</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226977</t>
+          <t>249588</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>273178</t>
+          <t>293971</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>476165</t>
+          <t>520190</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>438419</t>
+          <t>484550</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>508218</t>
+          <t>559194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>118224</t>
+          <t>126628</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95862</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150383</t>
+          <t>153909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>115352</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>109288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133782</t>
+          <t>146631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>233576</t>
+          <t>254231</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205097</t>
+          <t>226789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>267114</t>
+          <t>286407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>35305</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>51279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46614</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60066</t>
+          <t>65856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>78610</t>
+          <t>86003</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>69109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96543</t>
+          <t>105039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>172987</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134753</t>
+          <t>157425</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205772</t>
+          <t>214280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>350332</t>
+          <t>308705</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274562</t>
+          <t>278327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>572730</t>
+          <t>334366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>523319</t>
+          <t>493426</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>434878</t>
+          <t>456623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>745494</t>
+          <t>536265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1586406</t>
+          <t>1482791</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1420945</t>
+          <t>1421531</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1982282</t>
+          <t>1545644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1708273</t>
+          <t>1681192</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1559188</t>
+          <t>1627886</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2058334</t>
+          <t>1738580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3294679</t>
+          <t>3163983</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3033676</t>
+          <t>3083173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3770403</t>
+          <t>3242392</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1117308</t>
+          <t>1238058</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>882060</t>
+          <t>1175044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1226566</t>
+          <t>1298515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1106438</t>
+          <t>1225591</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>903576</t>
+          <t>1179064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1200734</t>
+          <t>1280649</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2223746</t>
+          <t>2463649</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1924680</t>
+          <t>2391192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2398106</t>
+          <t>2541756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>543192</t>
+          <t>579808</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>422776</t>
+          <t>525315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>612537</t>
+          <t>635282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>442137</t>
+          <t>462121</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>367253</t>
+          <t>421649</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>534854</t>
+          <t>503081</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>985329</t>
+          <t>1041929</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>865760</t>
+          <t>975709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1112570</t>
+          <t>1114467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
